--- a/assets/templates/algo_en_voice_reg_boundary_delete.xlsx
+++ b/assets/templates/algo_en_voice_reg_boundary_delete.xlsx
@@ -1309,7 +1309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="10" customWidth="1" style="29" min="1" max="1"/>
@@ -1924,16 +1924,16 @@
     </row>
     <row r="19" ht="16.5" customHeight="1">
       <c r="A19" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Learn Command</t>
+          <t>Start Study Light</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Learn Command</t>
+          <t>Start Study Light</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Please say the command to learn</t>
+          <t>Okay</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1953,27 +1953,27 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A5 FA 00 81 50 00 70 FB</t>
+          <t>A5 FA 00 81 57 00 77 FB</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>A5 FA 00 82 50 00 71 FB</t>
+          <t>A5 FA 00 82 57 00 78 FB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Learn Wake Word</t>
+          <t>Stop Study Light</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Learn Wake Word</t>
+          <t>Stop Study Light</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Please say the wake word to learn</t>
+          <t>Okay</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1993,27 +1993,27 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>A5 FA 00 81 51 00 71 FB</t>
+          <t>A5 FA 00 81 58 00 78 FB</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>A5 FA 00 82 51 00 72 FB</t>
+          <t>A5 FA 00 82 58 00 79 FB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Delete Command</t>
+          <t>Short Word</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Delete Command</t>
+          <t>Short Word</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Please say the command to delete</t>
+          <t>Short boundary sample</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2033,27 +2033,27 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>A5 FA 00 81 52 00 72 FB</t>
+          <t>A5 FA 00 81 61 00 81 FB</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>A5 FA 00 82 52 00 73 FB</t>
+          <t>A5 FA 00 82 61 00 82 FB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Delete Wake Word</t>
+          <t>Very Long Command Sample</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Delete Wake Word</t>
+          <t>Very Long Command Sample</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Please say the wake word to delete</t>
+          <t>Long boundary sample</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2073,290 +2073,10 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>A5 FA 00 81 53 00 73 FB</t>
+          <t>A5 FA 00 81 62 00 82 FB</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
-        <is>
-          <t>A5 FA 00 82 53 00 74 FB</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>54</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Delete All Commands</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Delete All Commands</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>命令词</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>All commands deleted</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>主</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>A5 FA 00 81 54 00 74 FB</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>A5 FA 00 82 54 00 75 FB</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>55</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Exit Learning</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Exit Learning</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>命令词</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Learning exited</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>主</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>A5 FA 00 81 55 00 75 FB</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>A5 FA 00 82 55 00 76 FB</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>56</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Exit Deletion</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Exit Deletion</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>命令词</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Deletion exited</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>主</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>A5 FA 00 81 56 00 76 FB</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>A5 FA 00 82 56 00 77 FB</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>57</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Start Study Light</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Start Study Light</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>命令词</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Okay</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>主</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>A5 FA 00 81 57 00 77 FB</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>A5 FA 00 82 57 00 78 FB</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>58</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Stop Study Light</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Stop Study Light</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>命令词</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Okay</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>主</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>A5 FA 00 81 58 00 78 FB</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>A5 FA 00 82 58 00 79 FB</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>61</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Short Word</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Short Word</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>命令词</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Short boundary sample</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>主</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>A5 FA 00 81 61 00 81 FB</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>A5 FA 00 82 61 00 82 FB</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>62</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Very Long Command Sample</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Very Long Command Sample</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>命令词</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Long boundary sample</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>主</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>A5 FA 00 81 62 00 82 FB</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
         <is>
           <t>A5 FA 00 82 62 00 83 FB</t>
         </is>
